--- a/CYP3A4_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A4_Allele_def_rs_excluidos.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7995" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
     <sheet name="Filtrada" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="104">
   <si>
     <t>rsID</t>
   </si>
@@ -250,9 +250,6 @@
     <t>*48</t>
   </si>
   <si>
-    <t>rs</t>
-  </si>
-  <si>
     <t>MAF European (non-finnish)</t>
   </si>
   <si>
@@ -311,6 +308,30 @@
   </si>
   <si>
     <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr7%3A99770117%2D99770317&amp;hgsid=3901234605_qqKm05HEwaXIjv74mkmc2GxejozW</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr7%3A99758128%2D99758328&amp;hgsid=3905088737_pHon3US2eHCMjb3TYxYKjOYvbQTe</t>
+  </si>
+  <si>
+    <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr7%3A99762134%2D99762334&amp;hgsid=3905090717_r2M3rfItOa7Ml3DzRhu73WCCPu4N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de datos </t>
+  </si>
+  <si>
+    <t>GenomAD</t>
+  </si>
+  <si>
+    <t>UCSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSC </t>
+  </si>
+  <si>
+    <t>rs/*alelo</t>
   </si>
 </sst>
 </file>
@@ -342,7 +363,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,6 +373,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,7 +402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -378,9 +411,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -397,7 +432,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -684,7 +719,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1144,14 +1179,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="26" max="26" width="13.7109375" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" customWidth="1"/>
+    <col min="27" max="28" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,21 +1263,24 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1319,7 +1357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1333,10 +1371,13 @@
         <v>3.0519999999999999E-5</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1350,10 +1391,13 @@
         <v>4.7840000000000001E-3</v>
       </c>
       <c r="AB5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -1367,10 +1411,13 @@
         <v>1.6950000000000001E-6</v>
       </c>
       <c r="AB6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1384,10 +1431,13 @@
         <v>5.0600000000000005E-4</v>
       </c>
       <c r="AB7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -1401,10 +1451,13 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1418,10 +1471,13 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -1435,10 +1491,13 @@
         <v>3.2209999999999998E-5</v>
       </c>
       <c r="AB10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -1452,24 +1511,33 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="Z12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -1483,10 +1551,13 @@
         <v>1.102E-5</v>
       </c>
       <c r="AB13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1500,10 +1571,13 @@
         <v>0</v>
       </c>
       <c r="AB14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1517,10 +1591,13 @@
         <v>2.7970000000000002E-5</v>
       </c>
       <c r="AB15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1534,10 +1611,13 @@
         <v>5.6780000000000002E-5</v>
       </c>
       <c r="AB16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -1551,10 +1631,13 @@
         <v>4.5769999999999997E-5</v>
       </c>
       <c r="AB17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -1568,10 +1651,13 @@
         <v>2.1189999999999999E-5</v>
       </c>
       <c r="AB18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -1585,32 +1671,35 @@
         <v>0</v>
       </c>
       <c r="AB19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="Z20" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>68</v>
       </c>
       <c r="G21" t="s">
         <v>27</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="Z21" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1624,10 +1713,13 @@
         <v>3.3909999999999998E-6</v>
       </c>
       <c r="AB22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1641,56 +1733,80 @@
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
       <c r="U24" t="s">
         <v>30</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="Z24" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>73</v>
       </c>
       <c r="X25" t="s">
         <v>29</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="Z25" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB25" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>74</v>
       </c>
       <c r="T26" t="s">
         <v>28</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="Z26" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>75</v>
       </c>
       <c r="R27" t="s">
         <v>30</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="Z27" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA28">
+        <f>SUM(AA4:AA27)*100</f>
+        <v>0.55205460000000017</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AB12" r:id="rId1"/>
+    <hyperlink ref="AC12" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CYP3A4_Allele_def_rs_excluidos.xlsx
+++ b/CYP3A4_Allele_def_rs_excluidos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="105">
   <si>
     <t>rsID</t>
   </si>
@@ -316,9 +316,6 @@
     <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr7%3A99758128%2D99758328&amp;hgsid=3905088737_pHon3US2eHCMjb3TYxYKjOYvbQTe</t>
   </si>
   <si>
-    <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr7%3A99762134%2D99762334&amp;hgsid=3905090717_r2M3rfItOa7Ml3DzRhu73WCCPu4N</t>
-  </si>
-  <si>
     <t xml:space="preserve">Base de datos </t>
   </si>
   <si>
@@ -328,10 +325,16 @@
     <t>UCSC</t>
   </si>
   <si>
-    <t xml:space="preserve">UCSC </t>
-  </si>
-  <si>
     <t>rs/*alelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSC, dnSNP </t>
+  </si>
+  <si>
+    <t>https://genome.ucsc.edu/cgi-bin/hgTracks?db=hg38&amp;lastVirtModeType=default&amp;lastVirtModeExtraState=&amp;virtModeType=default&amp;virtMode=0&amp;nonVirtPosition=&amp;position=chr7%3A99762134%2D99762334&amp;hgsid=3905310761_mBEiZluaJcsgdiBAFvn1PaaSQQ53</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs1318364992</t>
   </si>
 </sst>
 </file>
@@ -363,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,6 +391,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -402,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -413,6 +422,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1179,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="26" max="26" width="13.7109375" customWidth="1"/>
@@ -1263,13 +1273,13 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>76</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>77</v>
@@ -1371,7 +1381,7 @@
         <v>3.0519999999999999E-5</v>
       </c>
       <c r="AB4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="s">
         <v>78</v>
@@ -1391,7 +1401,7 @@
         <v>4.7840000000000001E-3</v>
       </c>
       <c r="AB5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC5" t="s">
         <v>79</v>
@@ -1411,7 +1421,7 @@
         <v>1.6950000000000001E-6</v>
       </c>
       <c r="AB6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC6" t="s">
         <v>80</v>
@@ -1431,7 +1441,7 @@
         <v>5.0600000000000005E-4</v>
       </c>
       <c r="AB7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC7" t="s">
         <v>81</v>
@@ -1451,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC8" t="s">
         <v>82</v>
@@ -1471,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC9" t="s">
         <v>83</v>
@@ -1491,7 +1501,7 @@
         <v>3.2209999999999998E-5</v>
       </c>
       <c r="AB10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC10" t="s">
         <v>84</v>
@@ -1511,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC11" t="s">
         <v>85</v>
@@ -1531,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>95</v>
@@ -1551,7 +1561,7 @@
         <v>1.102E-5</v>
       </c>
       <c r="AB13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC13" t="s">
         <v>86</v>
@@ -1571,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC14" t="s">
         <v>87</v>
@@ -1591,7 +1601,7 @@
         <v>2.7970000000000002E-5</v>
       </c>
       <c r="AB15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC15" t="s">
         <v>88</v>
@@ -1611,13 +1621,13 @@
         <v>5.6780000000000002E-5</v>
       </c>
       <c r="AB16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC16" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -1631,13 +1641,13 @@
         <v>4.5769999999999997E-5</v>
       </c>
       <c r="AB17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -1651,13 +1661,13 @@
         <v>2.1189999999999999E-5</v>
       </c>
       <c r="AB18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -1671,13 +1681,13 @@
         <v>0</v>
       </c>
       <c r="AB19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1688,7 +1698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -1699,7 +1709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1713,13 +1723,13 @@
         <v>3.3909999999999998E-6</v>
       </c>
       <c r="AB22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC22" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1733,13 +1743,13 @@
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AC23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
@@ -1750,7 +1760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>73</v>
       </c>
@@ -1760,14 +1770,17 @@
       <c r="Z25" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
       <c r="AB25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AC25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1778,24 +1791,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>75</v>
       </c>
       <c r="R27" t="s">
         <v>30</v>
       </c>
-      <c r="Z27" s="5" t="s">
+      <c r="Z27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="AB27" t="s">
         <v>102</v>
       </c>
-      <c r="AC27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="Z28" t="s">
         <v>96</v>
       </c>
